--- a/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>GRAL</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,150 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
-        <v>45291</v>
-      </c>
       <c r="G7" s="2">
+        <v>45200</v>
+      </c>
+      <c r="H7" s="2">
         <v>45109</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45018</v>
       </c>
-      <c r="I7" s="2">
-        <v>44012</v>
-      </c>
       <c r="J7" s="2">
+        <v>44377</v>
+      </c>
+      <c r="K7" s="2">
         <v>43830</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E8" s="3">
         <v>32000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26700</v>
       </c>
-      <c r="F8" s="3">
-        <v>93100</v>
-      </c>
       <c r="G8" s="3">
+        <v>20700</v>
+      </c>
+      <c r="H8" s="3">
         <v>22400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19600</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
+      <c r="J8" s="3">
+        <v>300</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E9" s="3">
         <v>16400</v>
       </c>
-      <c r="E9" s="3">
-        <v>15200</v>
-      </c>
       <c r="F9" s="3">
-        <v>54800</v>
+        <v>48600</v>
       </c>
       <c r="G9" s="3">
+        <v>14300</v>
+      </c>
+      <c r="H9" s="3">
         <v>13200</v>
       </c>
-      <c r="H9" s="3">
-        <v>11800</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="I9" s="3">
+        <v>45300</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E10" s="3">
         <v>15600</v>
       </c>
-      <c r="E10" s="3">
-        <v>11500</v>
-      </c>
       <c r="F10" s="3">
-        <v>38300</v>
+        <v>-21900</v>
       </c>
       <c r="G10" s="3">
+        <v>6400</v>
+      </c>
+      <c r="H10" s="3">
         <v>9200</v>
       </c>
-      <c r="H10" s="3">
-        <v>7800</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="I10" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-1000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,37 +824,41 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E12" s="3">
         <v>94200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>101600</v>
       </c>
-      <c r="F12" s="3">
-        <v>338700</v>
-      </c>
       <c r="G12" s="3">
+        <v>80100</v>
+      </c>
+      <c r="H12" s="3">
         <v>88700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>85900</v>
       </c>
-      <c r="I12" s="3">
-        <v>84800</v>
-      </c>
       <c r="J12" s="3">
+        <v>55100</v>
+      </c>
+      <c r="K12" s="3">
         <v>159100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,23 +886,26 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1420900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>718500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -893,13 +913,16 @@
         <v>4</v>
       </c>
       <c r="J14" s="3">
+        <v>200</v>
+      </c>
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -910,7 +933,7 @@
         <v>33500</v>
       </c>
       <c r="F15" s="3">
-        <v>133900</v>
+        <v>40000</v>
       </c>
       <c r="G15" s="3">
         <v>33500</v>
@@ -919,16 +942,19 @@
         <v>33500</v>
       </c>
       <c r="I15" s="3">
-        <v>2400</v>
+        <v>39800</v>
       </c>
       <c r="J15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K15" s="3">
         <v>6700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,66 +963,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1673300</v>
+        <v>193200</v>
       </c>
       <c r="E17" s="3">
+        <v>252300</v>
+      </c>
+      <c r="F17" s="3">
         <v>254100</v>
       </c>
-      <c r="F17" s="3">
-        <v>1608500</v>
-      </c>
       <c r="G17" s="3">
+        <v>214600</v>
+      </c>
+      <c r="H17" s="3">
         <v>226800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>223700</v>
       </c>
-      <c r="I17" s="3">
-        <v>139200</v>
-      </c>
       <c r="J17" s="3">
+        <v>106500</v>
+      </c>
+      <c r="K17" s="3">
         <v>255700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1641300</v>
+        <v>-164500</v>
       </c>
       <c r="E18" s="3">
+        <v>-220400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-227400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1515400</v>
-      </c>
       <c r="G18" s="3">
+        <v>-193900</v>
+      </c>
+      <c r="H18" s="3">
         <v>-204400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-204100</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
+      <c r="I18" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-106100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1008,153 +1041,169 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>7800</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-300</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1599100</v>
+        <v>-131600</v>
       </c>
       <c r="E21" s="3">
-        <v>-184500</v>
+        <v>-186900</v>
       </c>
       <c r="F21" s="3">
-        <v>-1348900</v>
+        <v>-187400</v>
       </c>
       <c r="G21" s="3">
-        <v>-163700</v>
+        <v>-160600</v>
       </c>
       <c r="H21" s="3">
-        <v>-161900</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-171200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-164100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-103300</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-172400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1638500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-224500</v>
       </c>
-      <c r="F23" s="3">
-        <v>-1507600</v>
-      </c>
       <c r="G23" s="3">
+        <v>-910100</v>
+      </c>
+      <c r="H23" s="3">
         <v>-202800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-201700</v>
       </c>
-      <c r="I23" s="3">
-        <v>-136400</v>
-      </c>
       <c r="J23" s="3">
+        <v>-105700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-245100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-117100</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-53100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-5600</v>
       </c>
-      <c r="F24" s="3">
-        <v>-42000</v>
-      </c>
       <c r="G24" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="H24" s="3">
         <v>-9800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-8000</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1182,66 +1231,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-125700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1585300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-218900</v>
       </c>
-      <c r="F26" s="3">
-        <v>-1465700</v>
-      </c>
       <c r="G26" s="3">
+        <v>-891400</v>
+      </c>
+      <c r="H26" s="3">
         <v>-193000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-193700</v>
       </c>
-      <c r="I26" s="3">
-        <v>-136400</v>
-      </c>
       <c r="J26" s="3">
+        <v>-105800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-244900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-125700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1585300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-218900</v>
       </c>
-      <c r="F27" s="3">
-        <v>-1465700</v>
-      </c>
       <c r="G27" s="3">
+        <v>-891400</v>
+      </c>
+      <c r="H27" s="3">
         <v>-193000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-193700</v>
       </c>
-      <c r="I27" s="3">
-        <v>-136400</v>
-      </c>
       <c r="J27" s="3">
+        <v>-105800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-244900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1269,8 +1327,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1298,8 +1359,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1327,8 +1391,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1356,66 +1423,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2800</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-7800</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-1500</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>300</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-125700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1585300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-218900</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1465700</v>
-      </c>
       <c r="G33" s="3">
+        <v>-891400</v>
+      </c>
+      <c r="H33" s="3">
         <v>-193000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-193700</v>
       </c>
-      <c r="I33" s="3">
-        <v>-136400</v>
-      </c>
       <c r="J33" s="3">
+        <v>-105800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-244900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1443,71 +1519,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-125700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1585300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-218900</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1465700</v>
-      </c>
       <c r="G35" s="3">
+        <v>-891400</v>
+      </c>
+      <c r="H35" s="3">
         <v>-193000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-193700</v>
       </c>
-      <c r="I35" s="3">
-        <v>-136400</v>
-      </c>
       <c r="J35" s="3">
+        <v>-105800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-244900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
-        <v>45291</v>
-      </c>
       <c r="G38" s="2">
+        <v>45200</v>
+      </c>
+      <c r="H38" s="2">
         <v>45109</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45018</v>
       </c>
-      <c r="I38" s="2">
-        <v>44012</v>
-      </c>
       <c r="J38" s="2">
+        <v>44377</v>
+      </c>
+      <c r="K38" s="2">
         <v>43830</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1519,8 +1604,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1532,20 +1618,21 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>853600</v>
+      </c>
+      <c r="E41" s="3">
         <v>958800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>199700</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1555,14 +1642,17 @@
       <c r="I41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
+      <c r="J41" s="3">
+        <v>578100</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1590,19 +1680,22 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>44200</v>
+        <v>19700</v>
       </c>
       <c r="E43" s="3">
-        <v>41500</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
+        <v>18700</v>
+      </c>
+      <c r="F43" s="3">
+        <v>15000</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
@@ -1613,54 +1706,60 @@
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+      <c r="J43" s="3">
+        <v>400</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15600</v>
+        <v>21200</v>
       </c>
       <c r="E45" s="3">
-        <v>17200</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
+        <v>25500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>21600</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
@@ -1677,20 +1776,23 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>909700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1018700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>258500</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>4</v>
       </c>
@@ -1700,55 +1802,61 @@
       <c r="I46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
+      <c r="J46" s="3">
+        <v>590300</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>144500</v>
+      </c>
+      <c r="E48" s="3">
         <v>152500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>160800</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>4</v>
       </c>
@@ -1758,43 +1866,49 @@
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+      <c r="J48" s="3">
+        <v>134600</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2051500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2086100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3541600</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1822,8 +1936,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1851,20 +1968,23 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E52" s="3">
         <v>12400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12000</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
@@ -1874,14 +1994,17 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3">
+        <v>8100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1909,20 +2032,23 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3118000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3269600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3972900</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>4</v>
       </c>
@@ -1932,14 +2058,17 @@
       <c r="I54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
+      <c r="J54" s="3">
+        <v>733000</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1951,8 +2080,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1964,20 +2094,21 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E57" s="3">
         <v>16200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11800</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>4</v>
       </c>
@@ -1987,25 +2118,28 @@
       <c r="I57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
+      <c r="J57" s="3">
+        <v>15200</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>13900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -2017,24 +2151,27 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>71900</v>
+        <v>1600</v>
       </c>
       <c r="E59" s="3">
-        <v>125800</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
+        <v>1400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1900</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
@@ -2045,26 +2182,29 @@
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+      <c r="J59" s="3">
+        <v>2500</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E60" s="3">
         <v>88200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>137600</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2074,25 +2214,28 @@
       <c r="I60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
+      <c r="J60" s="3">
+        <v>65600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>58700</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>62200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2104,24 +2247,27 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>73600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>486300</v>
+        <v>2300</v>
       </c>
       <c r="E62" s="3">
-        <v>95800</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
+        <v>2000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1800</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
@@ -2132,14 +2278,17 @@
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="J62" s="3">
+        <v>3500</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2167,8 +2316,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2196,8 +2348,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2225,20 +2380,23 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>530300</v>
+      </c>
+      <c r="E66" s="3">
         <v>574500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>233500</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2248,14 +2406,17 @@
       <c r="I66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
+      <c r="J66" s="3">
+        <v>142800</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2267,8 +2428,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2296,8 +2458,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2325,8 +2490,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2349,13 +2517,16 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>1994900</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2383,20 +2554,23 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9706300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9580600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7995200</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2406,14 +2580,17 @@
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
+      <c r="J72" s="3">
+        <v>-1829500</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2441,8 +2618,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2470,8 +2650,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2499,37 +2682,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2587600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2695100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3739400</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
+      <c r="I76" s="3">
+        <v>4646200</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-1404700</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2557,71 +2746,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
-        <v>45291</v>
-      </c>
       <c r="G80" s="2">
+        <v>45200</v>
+      </c>
+      <c r="H80" s="2">
         <v>45109</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45018</v>
       </c>
-      <c r="I80" s="2">
-        <v>44012</v>
-      </c>
       <c r="J80" s="2">
+        <v>44377</v>
+      </c>
+      <c r="K80" s="2">
         <v>43830</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-125700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1585300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-218900</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1465700</v>
-      </c>
       <c r="G81" s="3">
+        <v>-891400</v>
+      </c>
+      <c r="H81" s="3">
         <v>-193000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-193700</v>
       </c>
-      <c r="I81" s="3">
-        <v>-136400</v>
-      </c>
       <c r="J81" s="3">
+        <v>-105800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-244900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2633,37 +2831,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>39400</v>
+        <v>4500</v>
       </c>
       <c r="E83" s="3">
-        <v>40000</v>
+        <v>5300</v>
       </c>
       <c r="F83" s="3">
-        <v>158700</v>
+        <v>2500</v>
       </c>
       <c r="G83" s="3">
-        <v>39100</v>
+        <v>2500</v>
       </c>
       <c r="H83" s="3">
-        <v>39800</v>
+        <v>1600</v>
       </c>
       <c r="I83" s="3">
-        <v>4300</v>
+        <v>1700</v>
       </c>
       <c r="J83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K83" s="3">
         <v>10300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2691,8 +2893,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2720,8 +2925,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2749,8 +2957,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2778,8 +2989,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2807,37 +3021,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-104600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-171800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-207300</v>
       </c>
-      <c r="F89" s="3">
-        <v>-595800</v>
-      </c>
       <c r="G89" s="3">
+        <v>-157500</v>
+      </c>
+      <c r="H89" s="3">
         <v>-138900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-170500</v>
       </c>
-      <c r="I89" s="3">
-        <v>-101500</v>
-      </c>
       <c r="J89" s="3">
+        <v>-82200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-245800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-134800</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2849,37 +3069,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2500</v>
       </c>
-      <c r="F91" s="3">
-        <v>-7000</v>
-      </c>
       <c r="G91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1900</v>
-      </c>
       <c r="I91" s="3">
-        <v>-1200</v>
+        <v>-3100</v>
       </c>
       <c r="J91" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2907,8 +3131,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2936,37 +3163,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2500</v>
       </c>
-      <c r="F94" s="3">
-        <v>-12900</v>
-      </c>
       <c r="G94" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3100</v>
       </c>
-      <c r="I94" s="3">
-        <v>70500</v>
-      </c>
       <c r="J94" s="3">
+        <v>178600</v>
+      </c>
+      <c r="K94" s="3">
         <v>133000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2978,37 +3211,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3036,8 +3273,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3065,8 +3305,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3094,91 +3337,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>932300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>312000</v>
       </c>
-      <c r="F100" s="3">
-        <v>463800</v>
-      </c>
       <c r="G100" s="3">
+        <v>74000</v>
+      </c>
+      <c r="H100" s="3">
         <v>194900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>108900</v>
       </c>
-      <c r="I100" s="3">
-        <v>232500</v>
-      </c>
       <c r="J100" s="3">
+        <v>107700</v>
+      </c>
+      <c r="K100" s="3">
         <v>160300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-105300</v>
+      </c>
+      <c r="E102" s="3">
         <v>759100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>102100</v>
       </c>
-      <c r="F102" s="3">
-        <v>-144600</v>
-      </c>
       <c r="G102" s="3">
+        <v>-86800</v>
+      </c>
+      <c r="H102" s="3">
         <v>53300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-64500</v>
       </c>
-      <c r="I102" s="3">
-        <v>201500</v>
-      </c>
       <c r="J102" s="3">
+        <v>204100</v>
+      </c>
+      <c r="K102" s="3">
         <v>47700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>GRAL</t>
   </si>
@@ -656,163 +656,175 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45200</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="I7" s="2">
-        <v>45018</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E8" s="3">
         <v>28700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>30300</v>
+      </c>
+      <c r="I8" s="3">
         <v>20700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>22400</v>
       </c>
-      <c r="I8" s="3">
-        <v>19600</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>154600</v>
+      </c>
+      <c r="E9" s="3">
         <v>17400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>48600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>149400</v>
+      </c>
+      <c r="I9" s="3">
         <v>14300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>13200</v>
       </c>
-      <c r="I9" s="3">
-        <v>45300</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-116400</v>
+      </c>
+      <c r="E10" s="3">
         <v>11200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-21900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>-119100</v>
+      </c>
+      <c r="I10" s="3">
         <v>6400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>9200</v>
       </c>
-      <c r="I10" s="3">
-        <v>-25600</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -825,40 +837,44 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E12" s="3">
         <v>68500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>94200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>101600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>84100</v>
+      </c>
+      <c r="I12" s="3">
         <v>80100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>88700</v>
       </c>
-      <c r="I12" s="3">
-        <v>85900</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>55100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>159100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,72 +905,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E14" s="3">
         <v>19000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1420900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>17300</v>
+      </c>
+      <c r="I14" s="3">
         <v>718500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>33500</v>
+        <v>-100400</v>
       </c>
       <c r="E15" s="3">
         <v>33500</v>
       </c>
       <c r="F15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="G15" s="3">
         <v>40000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>-100400</v>
+      </c>
+      <c r="I15" s="3">
         <v>33500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>33500</v>
       </c>
-      <c r="I15" s="3">
-        <v>39800</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -964,72 +989,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>153700</v>
+      </c>
+      <c r="E17" s="3">
         <v>193200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>252300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>254100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>207600</v>
+      </c>
+      <c r="I17" s="3">
         <v>214600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>226800</v>
       </c>
-      <c r="I17" s="3">
-        <v>223700</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>106500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>255700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-115500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-164500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-220400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-227400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-177300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-193900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-204400</v>
       </c>
-      <c r="I18" s="3">
-        <v>-204000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-106100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1042,72 +1074,79 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-215300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-131600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-186900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-187400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-277500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-160600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-171200</v>
       </c>
-      <c r="I21" s="3">
-        <v>-164100</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-103300</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1132,78 +1171,87 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-172400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1638500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-224500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-193000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-910100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-202800</v>
       </c>
-      <c r="I23" s="3">
-        <v>-201700</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-105700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-245100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-117100</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-46700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-53100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I24" s="3">
         <v>-18600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-9800</v>
       </c>
-      <c r="I24" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1234,72 +1282,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-97100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-125700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1585300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-218900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-187500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-891400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-193000</v>
       </c>
-      <c r="I26" s="3">
-        <v>-193700</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-105800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-244900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-97100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-125700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1585300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-218900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-187500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-891400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-193000</v>
       </c>
-      <c r="I27" s="3">
-        <v>-193700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-105800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-244900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1330,8 +1387,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1362,8 +1422,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1394,8 +1457,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1426,72 +1492,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-97100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-125700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1585300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-218900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-187500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-891400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-193000</v>
       </c>
-      <c r="I33" s="3">
-        <v>-193700</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-105800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-244900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1522,77 +1597,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-97100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-125700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1585300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-218900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-187500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-891400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-193000</v>
       </c>
-      <c r="I35" s="3">
-        <v>-193700</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-105800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-244900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45200</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="I38" s="2">
-        <v>45018</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1605,8 +1689,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1619,45 +1704,49 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>214200</v>
+      </c>
+      <c r="E41" s="3">
         <v>853600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>958800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>199700</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
+      <c r="H41" s="3">
+        <v>97300</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>578100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>549200</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1683,40 +1772,46 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E43" s="3">
         <v>19700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>18700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3">
+        <v>23700</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1738,34 +1833,37 @@
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E45" s="3">
         <v>21200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3">
+        <v>21700</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
@@ -1779,40 +1877,46 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>819900</v>
+      </c>
+      <c r="E46" s="3">
         <v>909700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1018700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>258500</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
+      <c r="H46" s="3">
+        <v>156100</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>590300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1837,63 +1941,69 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>135400</v>
+      </c>
+      <c r="E48" s="3">
         <v>144500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>152500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>160800</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
+      <c r="H48" s="3">
+        <v>169400</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
         <v>134600</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2016900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2051500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2086100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3541600</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>3576200</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -1901,14 +2011,17 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1939,8 +2052,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1971,40 +2087,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E52" s="3">
         <v>12300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3">
+        <v>12200</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>8100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2035,40 +2157,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2983300</v>
+      </c>
+      <c r="E54" s="3">
         <v>3118000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3269600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3972900</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
+      <c r="H54" s="3">
+        <v>3913800</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>733000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2081,8 +2209,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2095,72 +2224,79 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E57" s="3">
         <v>7300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11800</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
+      <c r="H57" s="3">
+        <v>19700</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>15200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E58" s="3">
         <v>13500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>6100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2168,127 +2304,139 @@
         <v>1600</v>
       </c>
       <c r="E59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1900</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
+      <c r="H59" s="3">
+        <v>800</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E60" s="3">
         <v>94300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>88200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>137600</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
+      <c r="H60" s="3">
+        <v>163600</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>65600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E61" s="3">
         <v>58700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>66000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>69600</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>73600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="H62" s="3">
+        <v>1500</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>3500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2319,8 +2467,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2351,8 +2502,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2383,40 +2537,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>479900</v>
+      </c>
+      <c r="E66" s="3">
         <v>530300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>574500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>233500</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
+      <c r="H66" s="3">
+        <v>267600</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>142800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2429,8 +2589,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2461,8 +2622,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2493,8 +2657,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,16 +2684,19 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>1994900</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2557,40 +2727,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9803300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9706300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9580600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7995200</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
+      <c r="H72" s="3">
+        <v>-7776300</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1829500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2621,8 +2797,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2653,8 +2832,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2685,40 +2867,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2503400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2587600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2695100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3739400</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3">
-        <v>4646200</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="H76" s="3">
+        <v>3646200</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>-1404700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2749,77 +2937,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45200</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="I80" s="2">
-        <v>45018</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-97100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-125700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1585300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-218900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-187500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-891400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-193000</v>
       </c>
-      <c r="I81" s="3">
-        <v>-193700</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-105800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-244900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2832,40 +3029,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>5300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="I83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2896,8 +3097,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2928,8 +3132,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2960,8 +3167,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2992,8 +3202,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3024,40 +3237,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-104600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-171800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-207300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-128900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-157500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-138900</v>
       </c>
-      <c r="I89" s="3">
-        <v>-170500</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-82200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-245800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-134800</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3070,40 +3289,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="G91" s="3">
-        <v>-3100</v>
-      </c>
       <c r="H91" s="3">
-        <v>-2900</v>
+        <v>-3900</v>
       </c>
       <c r="I91" s="3">
         <v>-3100</v>
       </c>
       <c r="J91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-28700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3134,8 +3357,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3166,40 +3392,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-546100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-3100</v>
-      </c>
       <c r="H94" s="3">
-        <v>-2900</v>
+        <v>-3900</v>
       </c>
       <c r="I94" s="3">
         <v>-3100</v>
       </c>
       <c r="J94" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K94" s="3">
         <v>178600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>133000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3212,8 +3444,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3238,14 +3471,17 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3276,8 +3512,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3308,8 +3547,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3340,8 +3582,11 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3349,46 +3594,49 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>932300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>312000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>86000</v>
+      </c>
+      <c r="I100" s="3">
         <v>74000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>194900</v>
       </c>
-      <c r="I100" s="3">
-        <v>108900</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>107700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>160300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
@@ -3399,41 +3647,47 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-639900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-105300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>759100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>102100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-46600</v>
+      </c>
+      <c r="I102" s="3">
         <v>-86800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>53300</v>
       </c>
-      <c r="I102" s="3">
-        <v>-64500</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>204100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>47700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>28700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>GRAL</t>
   </si>
@@ -656,175 +656,188 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45109</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E8" s="3">
         <v>38300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>32000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E9" s="3">
         <v>154600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>48600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>149400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-116400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-21900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-119100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-1000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,43 +851,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E12" s="3">
         <v>49000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>68500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>94200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>101600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>84100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>80100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>88700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>55100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>159100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,78 +925,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>21500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1420900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>17300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>718500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E15" s="3">
         <v>-100400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>33500</v>
       </c>
       <c r="F15" s="3">
         <v>33500</v>
       </c>
       <c r="G15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="H15" s="3">
         <v>40000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-100400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>33500</v>
       </c>
       <c r="J15" s="3">
         <v>33500</v>
       </c>
       <c r="K15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="L15" s="3">
         <v>2500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -990,78 +1016,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>185500</v>
+      </c>
+      <c r="E17" s="3">
         <v>153700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>193200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>252300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>254100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>207600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>214600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>226800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>106500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>255700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-153600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-115500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-164500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-220400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-227400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-177300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-193900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-204400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-106100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1075,78 +1108,85 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-114900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-215300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-131600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-186900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-187400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-277500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-160600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-171200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-103300</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1174,84 +1214,93 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-146400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-127000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-172400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1638500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-224500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-193000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-910100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-202800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-105700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-245100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-117100</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-29900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-46700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-53100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-18600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-9800</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1285,78 +1334,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-97100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-125700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1585300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-218900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-187500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-891400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-193000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-105800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-244900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-97100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-125700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1585300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-218900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-187500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-891400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-193000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-105800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-244900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1390,8 +1448,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1425,8 +1486,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1460,8 +1524,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1495,78 +1562,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-97100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-125700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1585300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-218900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-187500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-891400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-193000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-105800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-244900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1600,83 +1676,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-97100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-125700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1585300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-218900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-187500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-891400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-193000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-105800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-244900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45200</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45109</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1690,8 +1775,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1705,52 +1791,56 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E41" s="3">
         <v>214200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>853600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>958800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>199700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>97300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>578100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>540700</v>
+      </c>
+      <c r="E42" s="3">
         <v>549200</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -1775,43 +1865,49 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E43" s="3">
         <v>24800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23700</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1836,38 +1932,41 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E45" s="3">
         <v>18600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
@@ -1880,43 +1979,49 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>727700</v>
+      </c>
+      <c r="E46" s="3">
         <v>819900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>909700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1018700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>258500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>156100</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>590300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1944,84 +2049,93 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>126900</v>
+      </c>
+      <c r="E48" s="3">
         <v>135400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>144500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>152500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>160800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>169400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>134600</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1982300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2016900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2051500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2086100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3541600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3576200</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2055,8 +2169,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2090,43 +2207,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E52" s="3">
         <v>11100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>8100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2160,43 +2283,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2847600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2983300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3118000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3269600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3972900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3913800</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>733000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2210,8 +2339,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2225,218 +2355,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E57" s="3">
         <v>4800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>15200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E58" s="3">
         <v>13300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>6100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="E59" s="3">
         <v>1600</v>
       </c>
       <c r="F59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G59" s="3">
         <v>1400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E60" s="3">
         <v>76900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>94300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>88200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>137600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>163600</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>65600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E61" s="3">
         <v>54900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>62200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>66000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>69600</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>73600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1500</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>3500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2470,8 +2619,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2505,8 +2657,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2540,43 +2695,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>433900</v>
+      </c>
+      <c r="E66" s="3">
         <v>479900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>530300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>574500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>233500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>267600</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>142800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2590,8 +2751,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2625,8 +2787,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2660,8 +2825,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2687,16 +2855,19 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>1994900</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2730,43 +2901,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9909500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9803300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9706300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9580600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7995200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7776300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1829500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2800,8 +2977,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2835,8 +3015,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2870,43 +3053,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2413700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2503400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2587600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2695100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3739400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3646200</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>-1404700</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2940,83 +3129,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45200</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45109</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-97100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-125700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1585300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-218900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-187500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-891400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-193000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-105800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-244900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3030,43 +3228,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E83" s="3">
         <v>5300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2500</v>
       </c>
       <c r="I83" s="3">
         <v>2500</v>
       </c>
       <c r="J83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K83" s="3">
         <v>1600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3100,8 +3302,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3135,8 +3340,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3170,8 +3378,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3205,8 +3416,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3240,43 +3454,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-93500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-104600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-171800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-207300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-128900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-157500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-138900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-82200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-245800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-134800</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3290,43 +3510,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3360,8 +3584,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3395,43 +3622,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-546100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>178600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>133000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3445,8 +3678,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3474,14 +3708,17 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3515,8 +3752,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3550,8 +3790,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3585,60 +3828,66 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>932300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>312000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>86000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>74000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>194900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>107700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>160300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>100</v>
       </c>
       <c r="G101" s="3">
         <v>100</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
@@ -3650,44 +3899,50 @@
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-80300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-639900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-105300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>759100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>102100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-46600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-86800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>53300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>204100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>47700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>28700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>GRAL</t>
   </si>
@@ -656,188 +656,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45200</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45109</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E8" s="3">
         <v>31800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E9" s="3">
         <v>51800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>154600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>48600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>149400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-19900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-116400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-21900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-119100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -852,46 +865,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E12" s="3">
         <v>53600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>49000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>68500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>94200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>101600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>84100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>80100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>88700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>55100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>159100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,84 +945,93 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>21500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1420900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>17300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>718500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E15" s="3">
         <v>39300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>-100400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>33500</v>
       </c>
       <c r="G15" s="3">
         <v>33500</v>
       </c>
       <c r="H15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="I15" s="3">
         <v>40000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-100400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>33500</v>
       </c>
       <c r="K15" s="3">
         <v>33500</v>
       </c>
       <c r="L15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="M15" s="3">
         <v>2500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1017,84 +1043,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>166400</v>
+      </c>
+      <c r="E17" s="3">
         <v>185500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>153700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>193200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>252300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>254100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>207600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>214600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>226800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>106500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>255700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-130900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-153600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-115500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-164500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-220400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-227400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-177300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-193900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-204400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-106100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1109,84 +1142,91 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-114900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-215300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-131600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-186900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-187400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-277500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-160600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-171200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-103300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1217,90 +1257,99 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-152900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-146400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-127000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-172400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1638500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-224500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-193000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-910100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-202800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-105700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-245100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-117100</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-40200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-29900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-46700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-53100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-18600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-9800</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1337,84 +1386,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-106200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-97100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-125700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1585300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-218900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-187500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-891400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-193000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-105800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-244900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-106200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-97100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-125700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1585300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-218900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-187500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-891400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-193000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-105800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-244900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1451,8 +1509,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1489,8 +1550,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,8 +1591,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1565,84 +1632,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-106200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-97100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-125700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1585300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-218900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-187500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-891400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-193000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-105800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-244900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1679,89 +1755,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-106200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-97100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-125700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1585300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-218900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-187500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-891400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-193000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-105800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-244900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45200</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45109</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1776,8 +1861,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1792,58 +1878,62 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>127400</v>
+      </c>
+      <c r="E41" s="3">
         <v>133900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>214200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>853600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>958800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>199700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>97300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>578100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>475300</v>
+      </c>
+      <c r="E42" s="3">
         <v>540700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>549200</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1868,46 +1958,52 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E43" s="3">
         <v>19300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23700</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1935,41 +2031,44 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E45" s="3">
         <v>18700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
@@ -1982,46 +2081,52 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>651800</v>
+      </c>
+      <c r="E46" s="3">
         <v>727700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>819900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>909700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1018700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>258500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>156100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>590300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2052,90 +2157,99 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E48" s="3">
         <v>126900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>135400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>144500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>152500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>160800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>169400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>134600</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1919700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1982300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2016900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2051500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2086100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3541600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3576200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2172,8 +2286,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2210,8 +2327,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2219,37 +2339,40 @@
         <v>10700</v>
       </c>
       <c r="E52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F52" s="3">
         <v>11100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>8100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2286,46 +2409,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2702600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2847600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2983300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3118000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3269600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3972900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3913800</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>733000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2340,8 +2469,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2356,236 +2486,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>15200</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E58" s="3">
         <v>13000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>6100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2500</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1600</v>
       </c>
       <c r="F59" s="3">
         <v>1600</v>
       </c>
       <c r="G59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H59" s="3">
         <v>1400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E60" s="3">
         <v>75000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>76900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>94300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>88200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>137600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>163600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>65600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E61" s="3">
         <v>51300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>62200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>66000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69600</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>73600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>3500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2622,8 +2771,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,8 +2812,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2698,46 +2853,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>387900</v>
+      </c>
+      <c r="E66" s="3">
         <v>433900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>479900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>530300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>574500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>233500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>267600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>142800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2752,8 +2913,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2790,8 +2952,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2828,8 +2993,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2858,16 +3026,19 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>1994900</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2904,46 +3075,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10023500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-9909500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-9803300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9706300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9580600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7995200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7776300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1829500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2980,8 +3157,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3018,8 +3198,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3056,46 +3239,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2314600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2413700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2503400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2587600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2695100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3739400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3646200</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>-1404700</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3132,89 +3321,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45200</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45109</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-106200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-97100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-125700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1585300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-218900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-187500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-891400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-193000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-105800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-244900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3229,46 +3427,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E83" s="3">
         <v>5400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2500</v>
       </c>
       <c r="J83" s="3">
         <v>2500</v>
       </c>
       <c r="K83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L83" s="3">
         <v>1600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3305,8 +3507,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3343,8 +3548,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3381,8 +3589,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3419,8 +3630,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3457,46 +3671,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-95000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-93500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-104600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-171800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-207300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-128900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-157500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-138900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-82200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-245800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-134800</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3511,46 +3731,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3587,8 +3811,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3625,46 +3852,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E94" s="3">
         <v>14600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-546100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>178600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>133000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3679,8 +3912,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3711,14 +3945,17 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3755,8 +3992,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3793,8 +4033,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3831,46 +4074,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>932300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>312000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>86000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>74000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>194900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>107700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>160300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3878,19 +4127,19 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>100</v>
       </c>
       <c r="H101" s="3">
         <v>100</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
@@ -3902,47 +4151,53 @@
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-80300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-639900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-105300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>759100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>102100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-46600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-86800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>204100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>47700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>28700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>GRAL</t>
   </si>
@@ -656,213 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45200</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E8" s="3">
         <v>36200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>31800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E9" s="3">
         <v>16500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18300</v>
       </c>
-      <c r="G9" s="3">
-        <v>154600</v>
-      </c>
       <c r="H9" s="3">
+        <v>20700</v>
+      </c>
+      <c r="I9" s="3">
         <v>17400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>149400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E10" s="3">
         <v>19700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13500</v>
       </c>
-      <c r="G10" s="3">
-        <v>-116400</v>
-      </c>
       <c r="H10" s="3">
+        <v>17500</v>
+      </c>
+      <c r="I10" s="3">
         <v>11200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-119100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E12" s="3">
         <v>48600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>46600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>53600</v>
       </c>
-      <c r="G12" s="3">
-        <v>49000</v>
-      </c>
       <c r="H12" s="3">
+        <v>39200</v>
+      </c>
+      <c r="I12" s="3">
         <v>78200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>94200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>101600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>84100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>80100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>88700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>55100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>159100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,52 +983,58 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
-        <v>21500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>40500</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>1420900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>17300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>718500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1026,7 +1048,7 @@
         <v>33500</v>
       </c>
       <c r="G15" s="3">
-        <v>-100400</v>
+        <v>33500</v>
       </c>
       <c r="H15" s="3">
         <v>33500</v>
@@ -1038,25 +1060,28 @@
         <v>33500</v>
       </c>
       <c r="K15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="L15" s="3">
         <v>-100400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>33500</v>
       </c>
       <c r="M15" s="3">
         <v>33500</v>
       </c>
       <c r="N15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="O15" s="3">
         <v>2500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E17" s="3">
         <v>161500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>166400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>185500</v>
       </c>
-      <c r="G17" s="3">
-        <v>153700</v>
-      </c>
       <c r="H17" s="3">
+        <v>134700</v>
+      </c>
+      <c r="I17" s="3">
         <v>212200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>252300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>254100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>207600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>214600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>226800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>106500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>255700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-124400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-125300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-130900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-153600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-115500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-96500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-183500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-220400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-227400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-177300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-193900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-204400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-106100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,96 +1208,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-91400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-98200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-120800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-215300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-150600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-186900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-193900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-277500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-160600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-171200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-103300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1302,102 +1341,111 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-116500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-118700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-152900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-146400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-127000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-172400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1638500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-224500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-193000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-910100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-202800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-105700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-245100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-117100</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-29700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-38900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-40200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-29900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-46700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-53100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-5600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-18600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-9800</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-99200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-89000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-114000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-106200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-97100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-125700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1585300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-218900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-187500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-891400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-193000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-105800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-244900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-99200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-89000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-114000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-106200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-97100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-125700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1585300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-218900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-187500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-891400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-193000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-105800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-244900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-99200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-89000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-114000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-106200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-97100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-125700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1585300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-218900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-187500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-891400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-193000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-105800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-244900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-99200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-89000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-114000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-106200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-97100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-125700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1585300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-218900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-187500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-891400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-193000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-105800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-244900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45200</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,70 +2050,74 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>249700</v>
+      </c>
+      <c r="E41" s="3">
         <v>126900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>127400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>133900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>214200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>853600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>958800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>199700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>578100</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>654700</v>
+      </c>
+      <c r="E42" s="3">
         <v>413200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>475300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>540700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>549200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2053,52 +2142,58 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16300</v>
+        <v>18300</v>
       </c>
       <c r="E43" s="3">
         <v>16300</v>
       </c>
       <c r="F43" s="3">
+        <v>16300</v>
+      </c>
+      <c r="G43" s="3">
         <v>19300</v>
       </c>
-      <c r="G43" s="3">
-        <v>24800</v>
-      </c>
       <c r="H43" s="3">
+        <v>20300</v>
+      </c>
+      <c r="I43" s="3">
         <v>19700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23700</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2132,47 +2227,50 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3">
         <v>1900</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E45" s="3">
         <v>18400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2185,52 +2283,58 @@
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>953800</v>
+      </c>
+      <c r="E46" s="3">
         <v>589400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>651800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>727700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>819900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>909700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1018700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>258500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>156100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>590300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2267,102 +2371,111 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>103900</v>
+      </c>
+      <c r="E48" s="3">
         <v>112200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>120200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>126900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>135400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>144500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>152500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>160800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>169400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>134600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1850600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1885100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1919700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1982300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2016900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2051500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2086100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3541600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3576200</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,52 +2565,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E52" s="3">
         <v>14300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>10700</v>
       </c>
       <c r="F52" s="3">
         <v>10700</v>
       </c>
       <c r="G52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="H52" s="3">
         <v>11100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>8100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2922000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2601000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2702600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2847600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2983300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3118000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3269600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3972900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3913800</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>733000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,96 +2746,103 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>15200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E58" s="3">
         <v>14000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>6100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2714,131 +2850,140 @@
         <v>1900</v>
       </c>
       <c r="E59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1600</v>
       </c>
       <c r="H59" s="3">
         <v>1600</v>
       </c>
       <c r="I59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>2500</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E60" s="3">
         <v>77400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>76900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>94300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>137600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>163600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>65600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E61" s="3">
         <v>44600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>51300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>58700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>62200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>66000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>69600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>73600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2846,43 +2991,46 @@
         <v>2800</v>
       </c>
       <c r="E62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F62" s="3">
         <v>2600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>3500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>344200</v>
+      </c>
+      <c r="E66" s="3">
         <v>361100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>387900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>433900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>479900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>530300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>574500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>233500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>267600</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>142800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3199,16 +3366,19 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>1994900</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10211700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10112500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10023500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9909500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9803300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-9706300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9580600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7995200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7776300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-1829500</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2577900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2240000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2314600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2413700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2503400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2587600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2695100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3739400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3646200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>-1404700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45200</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-99200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-89000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-114000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-106200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-97100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-125700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1585300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-218900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-187500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-891400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-193000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-105800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-244900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,52 +3823,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E83" s="3">
         <v>4600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2500</v>
       </c>
       <c r="L83" s="3">
         <v>2500</v>
       </c>
       <c r="M83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-63800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-63200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-77000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-95000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-93500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-104600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-171800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-207300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-128900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-157500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-138900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-82200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-245800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-134800</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,52 +4171,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-400</v>
       </c>
       <c r="F91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-236700</v>
+      </c>
+      <c r="E94" s="3">
         <v>66700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>70400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>14600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-546100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>178600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>133000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4184,14 +4417,17 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,13 +4564,16 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>423300</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>4</v>
@@ -4336,64 +4581,67 @@
       <c r="F100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>932300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>312000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>86000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>74000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>194900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>107700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>160300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
       </c>
       <c r="J101" s="3">
         <v>100</v>
       </c>
       <c r="K101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4405,53 +4653,59 @@
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E102" s="3">
         <v>3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-80300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-639900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-105300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>759100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>102100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-46600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-86800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>204100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>47700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>28700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>GRAL</t>
   </si>
@@ -656,225 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45200</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45109</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E8" s="3">
         <v>43600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>36200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>31800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>38300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E9" s="3">
         <v>21300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>149400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E10" s="3">
         <v>22300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-119100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +904,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E12" s="3">
         <v>46900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>48600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>46600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>53600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>39200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>78200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>94200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>101600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>84100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>80100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>88700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>55100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>159100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,55 +1002,61 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>28000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>40500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>1420900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>17300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>718500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1063,25 +1085,28 @@
         <v>33500</v>
       </c>
       <c r="L15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="M15" s="3">
         <v>-100400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>33500</v>
       </c>
       <c r="N15" s="3">
         <v>33500</v>
       </c>
       <c r="O15" s="3">
+        <v>33500</v>
+      </c>
+      <c r="P15" s="3">
         <v>2500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>176600</v>
+      </c>
+      <c r="E17" s="3">
         <v>168000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>161500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>166400</v>
       </c>
-      <c r="G17" s="3">
-        <v>185500</v>
-      </c>
       <c r="H17" s="3">
+        <v>185400</v>
+      </c>
+      <c r="I17" s="3">
         <v>134700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>212200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>252300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>254100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>207600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>214600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>226800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>106500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>255700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-135800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-124400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-125300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-130900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-153600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-96500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-183500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-220400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-227400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-177300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-193900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-204400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-106100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,102 +1241,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-91000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-91400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-98200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-120800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-120700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-62400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-150600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-186900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-193900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-277500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-160600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-171200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-103300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1344,108 +1383,117 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-127500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-116500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-118700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-152900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-146400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-127000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-172400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1638500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-224500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-193000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-910100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-202800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-105700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-245100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-117100</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-17300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-29700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-38900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-40200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-29900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-46700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-53100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-18600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-9800</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-99200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-89000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-114000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-106200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-97100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-125700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1585300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-218900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-187500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-891400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-193000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-105800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-244900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-99200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-89000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-114000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-106200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-97100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-125700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1585300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-218900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-187500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-891400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-193000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-105800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-244900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-99200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-89000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-114000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-106200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-97100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-125700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1585300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-218900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-187500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-891400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-193000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-105800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-244900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-99200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-89000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-114000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-106200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-97100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-125700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1585300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-218900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-187500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-891400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-193000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-105800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-244900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45200</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45109</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,76 +2136,80 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E41" s="3">
         <v>249700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>126900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>127400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>133900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>214200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>853600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>958800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>199700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>578100</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>753800</v>
+      </c>
+      <c r="E42" s="3">
         <v>654700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>413200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>475300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>540700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>549200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2145,55 +2234,61 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E43" s="3">
         <v>18300</v>
-      </c>
-      <c r="E43" s="3">
-        <v>16300</v>
       </c>
       <c r="F43" s="3">
         <v>16300</v>
       </c>
       <c r="G43" s="3">
+        <v>16300</v>
+      </c>
+      <c r="H43" s="3">
         <v>19300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23700</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2230,50 +2325,53 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>1900</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E45" s="3">
         <v>16000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2286,55 +2384,61 @@
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>877300</v>
+      </c>
+      <c r="E46" s="3">
         <v>953800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>589400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>651800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>727700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>819900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>909700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1018700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>258500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>156100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>590300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2374,108 +2478,117 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E48" s="3">
         <v>103900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>112200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>120200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>126900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>135400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>144500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>152500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>160800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>169400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>134600</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1816000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1850600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1885100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1919700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1982300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2016900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2051500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2086100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3541600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3576200</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,55 +2684,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E52" s="3">
         <v>13700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>10700</v>
       </c>
       <c r="G52" s="3">
         <v>10700</v>
       </c>
       <c r="H52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I52" s="3">
         <v>11100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>8100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2803500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2922000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2601000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2702600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2847600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2983300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3118000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3269600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3972900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3913800</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>733000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,290 +2876,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>15200</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E58" s="3">
         <v>11700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>6100</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E59" s="3">
         <v>1900</v>
       </c>
       <c r="F59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1600</v>
       </c>
       <c r="I59" s="3">
         <v>1600</v>
       </c>
       <c r="J59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>2500</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E60" s="3">
         <v>79700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>77400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>70600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>75000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>76900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>94300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>88200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>137600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>163600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>65600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E61" s="3">
         <v>43100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>48500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>51300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>62200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>66000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>69600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>73600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="E62" s="3">
         <v>2800</v>
       </c>
       <c r="F62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>3500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>302800</v>
+      </c>
+      <c r="E66" s="3">
         <v>344200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>361100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>387900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>433900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>479900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>530300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>574500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>233500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>267600</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>142800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3369,16 +3536,19 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>1994900</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10304900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10211700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10112500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10023500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9909500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-9803300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-9706300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9580600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7995200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7776300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-1829500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2500700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2577900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2240000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2314600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2413700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2503400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2587600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2695100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3739400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3646200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P76" s="3">
         <v>-1404700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45200</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45109</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-99200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-89000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-114000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-106200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-97100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-125700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1585300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-218900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-187500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-891400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-193000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-105800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-244900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-117200</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4021,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E83" s="3">
         <v>4900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>2500</v>
       </c>
       <c r="M83" s="3">
         <v>2500</v>
       </c>
       <c r="N83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O83" s="3">
         <v>1600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-87000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-63800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-63200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-77000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-95000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-93500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-104600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-171800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-207300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-128900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-157500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-138900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-82200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-245800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-134800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4391,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-400</v>
       </c>
       <c r="F91" s="3">
         <v>-400</v>
       </c>
       <c r="G91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-93400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-236700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>66700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>70400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>14600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-546100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>178600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>133000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4420,14 +4653,17 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,84 +4809,90 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
         <v>423300</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>932300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>312000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>86000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>74000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>194900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>107700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>160300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>100</v>
       </c>
       <c r="K101" s="3">
         <v>100</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4656,56 +4904,62 @@
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-180400</v>
+      </c>
+      <c r="E102" s="3">
         <v>122800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-80300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-639900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-105300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>759100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>102100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-46600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-86800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>53300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>204100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>47700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28700</v>
       </c>
     </row>
